--- a/instruction_data/templates/staff_lookup.xlsx
+++ b/instruction_data/templates/staff_lookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyle/projects/onesky_financial_agent/instruction_data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD6358C-2848-2C49-A612-CC6C57DE8982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132A6BB5-F74B-B14F-B393-8E0756093C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15520" xr2:uid="{3062CD22-B80D-024F-9F2A-073A11E13FE5}"/>
   </bookViews>
@@ -274,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,7 +778,7 @@
         <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
